--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008423128287666226</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18867228</v>
+        <v>4447195</v>
       </c>
       <c r="L2" t="n">
-        <v>11502771</v>
+        <v>2550984</v>
       </c>
       <c r="M2" t="n">
-        <v>2944109</v>
+        <v>615381</v>
       </c>
       <c r="N2" t="n">
-        <v>165298</v>
+        <v>29668</v>
       </c>
       <c r="O2" t="n">
-        <v>1758872</v>
+        <v>381714</v>
       </c>
       <c r="P2" t="n">
-        <v>661294</v>
+        <v>148234</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999998152256012</v>
+        <v>0.9999988675117493</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9387916326522827</v>
+        <v>0.8870503306388855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8587355017662048</v>
+        <v>0.7585613131523132</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8355218172073364</v>
+        <v>0.7009142637252808</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6205718517303467</v>
+        <v>0.4102493226528168</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8540635108947754</v>
+        <v>0.7449167966842651</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9126079678535461</v>
+        <v>0.8350458741188049</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -795,127 +795,127 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>18867228</v>
+        <v>4447195</v>
       </c>
       <c r="E3" t="n">
-        <v>1242211</v>
+        <v>567097</v>
       </c>
       <c r="F3" t="n">
-        <v>13025</v>
+        <v>7696</v>
       </c>
       <c r="G3" t="n">
-        <v>1779</v>
+        <v>858</v>
       </c>
       <c r="H3" t="n">
-        <v>697</v>
+        <v>376</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>40066441</v>
+        <v>10016615</v>
       </c>
       <c r="K3" t="n">
-        <v>43963307</v>
+        <v>10740102</v>
       </c>
       <c r="L3" t="n">
-        <v>50378412</v>
+        <v>12248773</v>
       </c>
       <c r="M3" t="n">
-        <v>61010955</v>
+        <v>15134421</v>
       </c>
       <c r="N3" t="n">
-        <v>64860945</v>
+        <v>16197760</v>
       </c>
       <c r="O3" t="n">
-        <v>62981542</v>
+        <v>15689511</v>
       </c>
       <c r="P3" t="n">
-        <v>64481882</v>
+        <v>16106972</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9375035762786865</v>
+        <v>0.8853259682655334</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8815904855728149</v>
+        <v>0.7803830504417419</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7897548675537109</v>
+        <v>0.6598616242408752</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4638134241104126</v>
+        <v>0.332634449005127</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8637528419494629</v>
+        <v>0.7493727803230286</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8552778363227844</v>
+        <v>0.7666773796081543</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1164072</v>
+        <v>538834</v>
       </c>
       <c r="E4" t="n">
-        <v>11502771</v>
+        <v>2550984</v>
       </c>
       <c r="F4" t="n">
-        <v>351705</v>
+        <v>160836</v>
       </c>
       <c r="G4" t="n">
-        <v>9284</v>
+        <v>5500</v>
       </c>
       <c r="H4" t="n">
-        <v>18796</v>
+        <v>11962</v>
       </c>
       <c r="I4" t="n">
-        <v>1121</v>
+        <v>771</v>
       </c>
       <c r="J4" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>1230126</v>
+        <v>566269</v>
       </c>
       <c r="L4" t="n">
-        <v>1892239</v>
+        <v>811940</v>
       </c>
       <c r="M4" t="n">
-        <v>579568</v>
+        <v>262588</v>
       </c>
       <c r="N4" t="n">
-        <v>101066</v>
+        <v>42649</v>
       </c>
       <c r="O4" t="n">
-        <v>300544</v>
+        <v>130711</v>
       </c>
       <c r="P4" t="n">
-        <v>63326</v>
+        <v>29282</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999991059303284</v>
+        <v>0.999999463558197</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9381471872329712</v>
+        <v>0.8861873149871826</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8700129985809326</v>
+        <v>0.7693175077438354</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8119938969612122</v>
+        <v>0.6797686219215393</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5308621525764465</v>
+        <v>0.3673873543739319</v>
       </c>
       <c r="V4" t="n">
-        <v>0.858880877494812</v>
+        <v>0.7471381425857544</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8830133676528931</v>
+        <v>0.7994025349617004</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>39378</v>
+        <v>16677</v>
       </c>
       <c r="E5" t="n">
-        <v>549793</v>
+        <v>211767</v>
       </c>
       <c r="F5" t="n">
-        <v>2944109</v>
+        <v>615381</v>
       </c>
       <c r="G5" t="n">
-        <v>40915</v>
+        <v>17507</v>
       </c>
       <c r="H5" t="n">
-        <v>146494</v>
+        <v>66851</v>
       </c>
       <c r="I5" t="n">
-        <v>7188</v>
+        <v>4408</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1257739</v>
+        <v>576034</v>
       </c>
       <c r="L5" t="n">
-        <v>1544978</v>
+        <v>717903</v>
       </c>
       <c r="M5" t="n">
-        <v>783768</v>
+        <v>317210</v>
       </c>
       <c r="N5" t="n">
-        <v>191091</v>
+        <v>59523</v>
       </c>
       <c r="O5" t="n">
-        <v>277442</v>
+        <v>127664</v>
       </c>
       <c r="P5" t="n">
-        <v>111898</v>
+        <v>45112</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9999995827674866</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9619117379188538</v>
+        <v>0.9300470948219299</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9473775029182434</v>
+        <v>0.9063147306442261</v>
       </c>
       <c r="T5" t="n">
-        <v>0.979127824306488</v>
+        <v>0.9644940495491028</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9955272078514099</v>
+        <v>0.9937431216239929</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9911512732505798</v>
+        <v>0.9841775298118591</v>
       </c>
       <c r="W5" t="n">
-        <v>0.997317373752594</v>
+        <v>0.9954442381858826</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>26516</v>
+        <v>10713</v>
       </c>
       <c r="E6" t="n">
-        <v>79751</v>
+        <v>19379</v>
       </c>
       <c r="F6" t="n">
-        <v>53266</v>
+        <v>18086</v>
       </c>
       <c r="G6" t="n">
-        <v>165298</v>
+        <v>29668</v>
       </c>
       <c r="H6" t="n">
-        <v>29784</v>
+        <v>10488</v>
       </c>
       <c r="I6" t="n">
-        <v>1762</v>
+        <v>855</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>19496</v>
+        <v>13087</v>
       </c>
       <c r="F7" t="n">
-        <v>157487</v>
+        <v>73457</v>
       </c>
       <c r="G7" t="n">
-        <v>47147</v>
+        <v>17859</v>
       </c>
       <c r="H7" t="n">
-        <v>1758872</v>
+        <v>381714</v>
       </c>
       <c r="I7" t="n">
-        <v>53228</v>
+        <v>23241</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>988</v>
+        <v>610</v>
       </c>
       <c r="F8" t="n">
-        <v>4085</v>
+        <v>2513</v>
       </c>
       <c r="G8" t="n">
-        <v>1941</v>
+        <v>925</v>
       </c>
       <c r="H8" t="n">
-        <v>104773</v>
+        <v>41034</v>
       </c>
       <c r="I8" t="n">
-        <v>661294</v>
+        <v>148234</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
